--- a/public/templates/programs-template.xlsx
+++ b/public/templates/programs-template.xlsx
@@ -397,12 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:G8"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,6 +421,15 @@
       <c r="D1" t="str">
         <v>选手姓名</v>
       </c>
+      <c r="E1" t="str">
+        <v>表演时长</v>
+      </c>
+      <c r="F1" t="str">
+        <v>道具需求</v>
+      </c>
+      <c r="G1" t="str">
+        <v>特殊要求</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +444,15 @@
       <c r="D2" t="str">
         <v>张三</v>
       </c>
+      <c r="E2" t="str">
+        <v>5分钟</v>
+      </c>
+      <c r="F2" t="str">
+        <v>无</v>
+      </c>
+      <c r="G2" t="str">
+        <v>需要暗场灯光</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -446,6 +467,15 @@
       <c r="D3" t="str">
         <v>李四</v>
       </c>
+      <c r="E3" t="str">
+        <v>4分钟</v>
+      </c>
+      <c r="F3" t="str">
+        <v>话筒一个</v>
+      </c>
+      <c r="G3" t="str">
+        <v>需要背景音乐</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -460,6 +490,15 @@
       <c r="D4" t="str">
         <v>王五</v>
       </c>
+      <c r="E4" t="str">
+        <v>6分钟</v>
+      </c>
+      <c r="F4" t="str">
+        <v>民族道具</v>
+      </c>
+      <c r="G4" t="str">
+        <v>需要彩色灯光</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -474,6 +513,15 @@
       <c r="D5" t="str">
         <v>赵六</v>
       </c>
+      <c r="E5" t="str">
+        <v>8分钟</v>
+      </c>
+      <c r="F5" t="str">
+        <v>小提琴</v>
+      </c>
+      <c r="G5" t="str">
+        <v>需要钢琴伴奏</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -488,6 +536,15 @@
       <c r="D6" t="str">
         <v>钱七</v>
       </c>
+      <c r="E6" t="str">
+        <v>10分钟</v>
+      </c>
+      <c r="F6" t="str">
+        <v>舞台道具</v>
+      </c>
+      <c r="G6" t="str">
+        <v>需要背景音效</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -502,6 +559,15 @@
       <c r="D7" t="str">
         <v>张三,李四,王五</v>
       </c>
+      <c r="E7" t="str">
+        <v>7分钟</v>
+      </c>
+      <c r="F7" t="str">
+        <v>话筒三个</v>
+      </c>
+      <c r="G7" t="str">
+        <v>需要合唱台</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -516,10 +582,19 @@
       <c r="D8" t="str">
         <v>王五,其他舞者</v>
       </c>
+      <c r="E8" t="str">
+        <v>9分钟</v>
+      </c>
+      <c r="F8" t="str">
+        <v>民族服装</v>
+      </c>
+      <c r="G8" t="str">
+        <v>需要大型舞台</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>